--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$31</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="290">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -423,33 +423,57 @@
     <t>List.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>List.extension:PatientModified</t>
+  </si>
+  <si>
+    <t>PatientModified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-patient-modified}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Extension Patient Modified</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Extension, die Angibt, ob in einer Ressource eine Änderung vom Patienten veranlasst wurde.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>List.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>List.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -457,6 +481,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -470,7 +497,7 @@
 </t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste (des Medikationsplans).</t>
+    <t>Business identifier</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -780,6 +807,9 @@
   </si>
   <si>
     <t>List.entry.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1226,12 +1256,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL30"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.04296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="24.61328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="23.04296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.14453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2145,7 +2175,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2164,17 +2194,15 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>134</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -2211,16 +2239,14 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>135</v>
@@ -2238,7 +2264,7 @@
         <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>21</v>
@@ -2249,43 +2275,41 @@
         <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2333,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2342,56 +2366,60 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2439,7 +2467,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2451,21 +2479,21 @@
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2473,32 +2501,30 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
@@ -2523,11 +2549,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2545,13 +2573,13 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
@@ -2605,39 +2633,35 @@
       <c r="N13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2670,18 +2694,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2689,64 +2713,66 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="U14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
       </c>
@@ -2763,10 +2789,10 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>85</v>
@@ -2781,15 +2807,15 @@
         <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2797,13 +2823,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -2812,17 +2838,15 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
+      <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
         <v>178</v>
       </c>
@@ -2831,14 +2855,14 @@
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="S15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="U15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2849,13 +2873,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2873,7 +2897,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2888,18 +2912,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2922,26 +2946,26 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>21</v>
@@ -2959,13 +2983,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -2983,7 +3007,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3004,7 +3028,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>193</v>
       </c>
@@ -3017,19 +3041,19 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>194</v>
@@ -3040,8 +3064,12 @@
       <c r="M17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="N17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3104,18 +3132,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3123,35 +3151,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O18" t="s" s="2">
         <v>204</v>
       </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3199,7 +3223,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3229,7 +3253,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3248,19 +3272,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3324,53 +3348,53 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL19" t="s" s="2">
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>215</v>
       </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3395,13 +3419,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3419,7 +3443,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3434,10 +3458,10 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3468,16 +3492,20 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3501,13 +3529,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -3531,7 +3559,7 @@
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -3540,18 +3568,18 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3562,10 +3590,10 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
@@ -3574,17 +3602,15 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3633,7 +3659,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3642,24 +3668,24 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3670,10 +3696,10 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -3682,15 +3708,17 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3739,22 +3767,22 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3762,21 +3790,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -3788,17 +3816,15 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -3847,22 +3873,22 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3870,14 +3896,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>245</v>
+        <v>144</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3890,26 +3916,24 @@
         <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -3957,7 +3981,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3972,53 +3996,53 @@
         <v>136</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>128</v>
+        <v>248</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I26" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>252</v>
+        <v>147</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>253</v>
+        <v>148</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4043,11 +4067,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4065,33 +4091,33 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4099,85 +4125,81 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y27" s="2"/>
+      <c r="Z27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4186,13 +4208,13 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4220,28 +4242,32 @@
         <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="R28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4294,24 +4320,24 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4319,13 +4345,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4334,16 +4360,18 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4391,10 +4419,10 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>85</v>
@@ -4406,7 +4434,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4414,10 +4442,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4425,7 +4453,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>85</v>
@@ -4440,20 +4468,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>174</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4477,11 +4501,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4499,29 +4525,137 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y31" s="2"/>
+      <c r="Z31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL30">
+  <autoFilter ref="A1:AL31">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4531,7 +4665,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI29">
+  <conditionalFormatting sqref="A2:AI30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -592,7 +592,7 @@
 </t>
   </si>
   <si>
-    <t>Code, der den Typ der Liste beschreibt.</t>
+    <t>Code der den Medikationsplan identifiziert</t>
   </si>
   <si>
     <t>This code defines the purpose of the list - why it was created.</t>
@@ -704,13 +704,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|Device|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|Device)
 </t>
   </si>
   <si>
     <t>Ersteller des Medikationsplans und für den Inhalt verantwortlich. 
 Im Falle eines GDA: Eindeutig identifiziert über den GDA-Index und berechtigt auf die e-Medikation 
-des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. ELGA-Teilnehmer nur Ausübung seiner Teilnehmerrechte (Löschen von Einträgen).</t>
+des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -885,7 +885,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Kein Datum der Aufnahme bzw. Änderung des Eintrags im Medikationsplan. Das Datum ist nur im referenzierten Medikationsplaneintrag ersichtlich.</t>
+    <t>Kein Datum der Aufnahme des Eintrags im Medikationsplan. Das Datum ist nur im referenzierten Medikationsplaneintrag ersichtlich.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -1269,7 +1269,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="192.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="137.1640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1520,7 +1520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -1533,13 +1533,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -1628,7 +1628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>92</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>85</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -1750,7 +1750,7 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -1950,7 +1950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>113</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}at-emed-list-same-patient:Alle in der Liste referenzierten Patienten müssen gleich sein {subject.resolve() = entry.item.resolve().ofType(MedicationRequest).subject.resolve()}</t>
   </si>
   <si>
     <t>Act[classCode&lt;ORG,moodCode=EVN]</t>
@@ -457,7 +457,7 @@
 </t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation Extension Patient Modified</t>
+    <t>Boolean der angibt, ob diese Version des Plans durch Aktionen des Patienten verändert wurde (z.B. Einträge entfernt).</t>
   </si>
   <si>
     <t>AT ELGA e-Medikation Extension, die Angibt, ob in einer Ressource eine Änderung vom Patienten veranlasst wurde.</t>
@@ -570,7 +570,7 @@
 </t>
   </si>
   <si>
-    <t>Der Medikationsplan hat keinen Titel.</t>
+    <t>Descriptive name for the list</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -660,7 +660,7 @@
 </t>
   </si>
   <si>
-    <t>Es wird kein Behandlungskontext dokumentiert.</t>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>The encounter that is the context in which this list was created.</t>
@@ -704,13 +704,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|Device)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung)
 </t>
   </si>
   <si>
-    <t>Ersteller des Medikationsplans und für den Inhalt verantwortlich. 
-Im Falle eines GDA: Eindeutig identifiziert über den GDA-Index und berechtigt auf die e-Medikation 
-des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung.</t>
+    <t>Ersteller des Medikationsplans und für den Inhalt verantwortlich. Device nur für initiale Erstellung durch die Fachanwendung.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -731,7 +729,7 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge wird über die List.entries durch den Ersteller vorgegeben.</t>
+    <t>What order the list has</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -759,7 +757,7 @@
 </t>
   </si>
   <si>
-    <t>Keine Freitext-Anmerkungen im Medikationsplan.</t>
+    <t>Fachliche Begrüundung: Auf dieser Ebene keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests(Planeinträgen möglich)</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -860,7 +858,7 @@
 </t>
   </si>
   <si>
-    <t>Keine Verwendung im Medikationsplan (da list.mode immer working).</t>
+    <t>Fachliche Begründung: Keine Verwendung im Medikationsplan (da list.mode immer working).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -885,7 +883,8 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Kein Datum der Aufnahme des Eintrags im Medikationsplan. Das Datum ist nur im referenzierten Medikationsplaneintrag ersichtlich.</t>
+    <t>Fachliche Begründung: Kein Datum der initialen Aufnahme des Eintrags im Medikationsplan.
+Das Datum ist nur im referenzierten Medikationsplaneintrag ersichtlich.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -916,7 +915,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein</t>
+    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown | unavailable] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein | unavailable: Plan ist leer weil alle Einträge vom Patienten entfernt wurden</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -1269,7 +1268,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="137.1640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="201.5546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2270,7 +2269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
@@ -2826,7 +2825,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -289,7 +289,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown | unavailable] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein | unavailable: Plan ist leer weil alle Einträge vom Patienten entfernt wurden</t>
+    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown | unavailable] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein | unavailable: Plan ist leer weil alle Einträge entfernt wurden</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,8 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Der Medikationsplan wird durch eine List-Ressource abgebildet. 
-Diese enthält 0..* Einträge (List.entry), wobei jedes List.entry.item genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) beinhaltet.
+    <t>Der Medikationsplan wird durch eine List-Ressource abgebildet und enthält:
+- 0..* Einträge (List.entry). 
+Jedes List.entry.item enhält genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest).
 Die Reihung der List.entries bestimmt die Reihenfolge der Medikationsplaneinträge. 
 Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3917" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -680,17 +680,62 @@
 </t>
   </si>
   <si>
+    <t>List.extension:PatientModified.id</t>
+  </si>
+  <si>
+    <t>List.extension.id</t>
+  </si>
+  <si>
+    <t>List.extension:PatientModified.extension</t>
+  </si>
+  <si>
+    <t>List.extension.extension</t>
+  </si>
+  <si>
+    <t>List.extension:PatientModified.url</t>
+  </si>
+  <si>
+    <t>List.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-patient-modified</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>List.extension:PatientModified.value[x]</t>
+  </si>
+  <si>
+    <t>List.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
     <t>List.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -718,7 +763,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplans. Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
+    <t>Status des Medikationsplans. Fixer Wert: current</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -727,7 +772,13 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListStatusVS</t>
+    <t>current</t>
+  </si>
+  <si>
+    <t>The current state of the list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-status|4.0.1</t>
   </si>
   <si>
     <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
@@ -930,10 +981,6 @@
   </si>
   <si>
     <t>List.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>If this coding was chosen directly by the user</t>
@@ -1422,6 +1469,9 @@
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1928,10 +1978,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL110"/>
+  <dimension ref="A1:AL114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="31.48046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.80078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="31.48046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.14453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2957,10 +3007,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>86</v>
@@ -4345,43 +4395,39 @@
         <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>100</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4429,22 +4475,22 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>215</v>
+        <v>102</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -4452,10 +4498,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4466,7 +4512,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4478,13 +4524,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>217</v>
+        <v>106</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4523,19 +4569,19 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>113</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4547,21 +4593,21 @@
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4578,22 +4624,22 @@
         <v>86</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4601,7 +4647,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4619,11 +4665,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4641,7 +4689,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>85</v>
@@ -4653,21 +4701,21 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4684,32 +4732,28 @@
         <v>86</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>21</v>
@@ -4727,13 +4771,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4751,10 +4795,10 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>85</v>
@@ -4766,18 +4810,18 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4788,30 +4832,28 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
+        <v>203</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>242</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4823,7 +4865,7 @@
         <v>21</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>21</v>
@@ -4859,33 +4901,33 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4893,35 +4935,31 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4945,13 +4983,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4969,13 +5007,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -4984,18 +5022,18 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5003,30 +5041,32 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5036,7 +5076,7 @@
         <v>21</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>21</v>
@@ -5051,13 +5091,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5075,10 +5115,10 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>85</v>
@@ -5087,61 +5127,63 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>103</v>
+        <v>244</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>106</v>
+        <v>161</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>21</v>
@@ -5159,57 +5201,57 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>113</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5217,13 +5259,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5232,19 +5274,17 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5257,7 +5297,7 @@
         <v>21</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>21</v>
@@ -5293,13 +5333,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5308,18 +5348,18 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5327,31 +5367,35 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>99</v>
+        <v>263</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5375,13 +5419,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5399,7 +5443,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5411,32 +5455,32 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>103</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5448,17 +5492,15 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5495,31 +5537,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>103</v>
@@ -5528,48 +5570,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>268</v>
+        <v>108</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5578,7 +5618,7 @@
         <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -5605,34 +5645,34 @@
         <v>21</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>113</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>273</v>
+        <v>103</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
@@ -5651,7 +5691,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>85</v>
@@ -5666,7 +5706,7 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>275</v>
@@ -5677,7 +5717,9 @@
       <c r="N35" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5725,13 +5767,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -5740,18 +5782,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5759,39 +5801,37 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
+        <v>101</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>21</v>
@@ -5833,7 +5873,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>285</v>
+        <v>102</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5845,55 +5885,55 @@
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>107</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5929,45 +5969,45 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>113</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>292</v>
+        <v>103</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5975,13 +6015,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -5990,19 +6030,19 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6012,7 +6052,7 @@
         <v>21</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>21</v>
@@ -6051,7 +6091,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6066,18 +6106,18 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6091,7 +6131,7 @@
         <v>85</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6103,17 +6143,15 @@
         <v>99</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6161,7 +6199,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6176,7 +6214,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -6184,10 +6222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6210,26 +6248,24 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>309</v>
+        <v>161</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>21</v>
+        <v>301</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
@@ -6271,7 +6307,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6286,18 +6322,18 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6311,25 +6347,27 @@
         <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>101</v>
+        <v>306</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6377,7 +6415,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>102</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6389,10 +6427,10 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>103</v>
+        <v>309</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6400,21 +6438,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6423,21 +6461,23 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>107</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6473,45 +6513,45 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>113</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>103</v>
+        <v>316</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6525,7 +6565,7 @@
         <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6537,15 +6577,17 @@
         <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6602,13 +6644,13 @@
         <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>186</v>
+        <v>323</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6627,7 +6669,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>85</v>
@@ -6642,18 +6684,20 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>127</v>
+        <v>325</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6677,13 +6721,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6701,7 +6745,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6716,18 +6760,18 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>186</v>
+        <v>330</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>21</v>
+        <v>331</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6741,26 +6785,24 @@
         <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>332</v>
+        <v>100</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6809,7 +6851,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>335</v>
+        <v>102</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6821,10 +6863,10 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>336</v>
+        <v>103</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6832,21 +6874,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6858,15 +6900,17 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6903,31 +6947,31 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>103</v>
@@ -6936,44 +6980,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>108</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>109</v>
+        <v>337</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7011,45 +7055,45 @@
         <v>21</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>113</v>
+        <v>338</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7063,29 +7107,27 @@
         <v>85</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O48" t="s" s="2">
         <v>343</v>
       </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7109,7 +7151,7 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="Y48" t="s" s="2">
         <v>344</v>
@@ -7148,18 +7190,18 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7173,7 +7215,7 @@
         <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7182,20 +7224,18 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>352</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7219,13 +7259,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7243,7 +7283,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7258,18 +7298,18 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7283,29 +7323,25 @@
         <v>85</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>357</v>
+        <v>100</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7317,7 +7353,7 @@
         <v>21</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>21</v>
@@ -7353,7 +7389,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>362</v>
+        <v>102</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7365,53 +7401,53 @@
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>363</v>
+        <v>103</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>107</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>108</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>367</v>
+        <v>109</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7425,7 +7461,7 @@
         <v>21</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>21</v>
@@ -7449,34 +7485,34 @@
         <v>21</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>369</v>
+        <v>113</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7484,10 +7520,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7504,22 +7540,26 @@
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>372</v>
+        <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7543,13 +7583,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7567,7 +7607,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7582,7 +7622,7 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7590,10 +7630,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7616,18 +7656,20 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>378</v>
+        <v>263</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7651,13 +7693,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7675,7 +7717,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7690,18 +7732,18 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7715,7 +7757,7 @@
         <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -7724,18 +7766,20 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7747,7 +7791,7 @@
         <v>21</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>21</v>
@@ -7783,7 +7827,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7798,18 +7842,18 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>186</v>
+        <v>379</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7820,27 +7864,29 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>390</v>
+        <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7853,7 +7899,7 @@
         <v>21</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>21</v>
@@ -7889,7 +7935,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7904,18 +7950,18 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7923,13 +7969,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -7938,20 +7984,16 @@
         <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -7999,7 +8041,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8014,32 +8056,32 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8048,20 +8090,18 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8109,7 +8149,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8124,18 +8164,18 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8155,18 +8195,20 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>100</v>
+        <v>401</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8215,7 +8257,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>102</v>
+        <v>404</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8227,10 +8269,10 @@
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -8238,21 +8280,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8264,17 +8306,15 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>106</v>
+        <v>406</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>107</v>
+        <v>407</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8311,45 +8351,45 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>113</v>
+        <v>405</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>103</v>
+        <v>409</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8372,18 +8412,20 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>99</v>
+        <v>412</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>319</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>320</v>
+        <v>414</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8431,7 +8473,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8440,32 +8482,32 @@
         <v>85</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>186</v>
+        <v>417</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>85</v>
@@ -8480,18 +8522,20 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>127</v>
+        <v>421</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>326</v>
+        <v>423</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8515,13 +8559,13 @@
         <v>21</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>21</v>
@@ -8539,7 +8583,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8554,18 +8598,18 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>186</v>
+        <v>426</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>21</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8579,26 +8623,24 @@
         <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>332</v>
+        <v>100</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8647,7 +8689,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>335</v>
+        <v>102</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8659,10 +8701,10 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>336</v>
+        <v>103</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>21</v>
@@ -8670,21 +8712,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -8696,15 +8738,17 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8741,31 +8785,31 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>103</v>
@@ -8774,44 +8818,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>108</v>
+        <v>336</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>109</v>
+        <v>337</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8849,45 +8893,45 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>113</v>
+        <v>338</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8901,29 +8945,27 @@
         <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O65" t="s" s="2">
         <v>343</v>
       </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -8947,7 +8989,7 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="Y65" t="s" s="2">
         <v>344</v>
@@ -8986,18 +9028,18 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>347</v>
+        <v>186</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9011,7 +9053,7 @@
         <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9020,20 +9062,18 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N66" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>352</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9057,13 +9097,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9081,7 +9121,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9096,18 +9136,18 @@
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9121,29 +9161,25 @@
         <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>357</v>
+        <v>100</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9155,7 +9191,7 @@
         <v>21</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>21</v>
@@ -9191,7 +9227,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>362</v>
+        <v>102</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9203,53 +9239,53 @@
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>363</v>
+        <v>103</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>365</v>
+        <v>107</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>366</v>
+        <v>108</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>367</v>
+        <v>109</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9263,7 +9299,7 @@
         <v>21</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>21</v>
@@ -9287,34 +9323,34 @@
         <v>21</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>369</v>
+        <v>113</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
@@ -9322,10 +9358,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9342,22 +9378,26 @@
         <v>21</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>372</v>
+        <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9381,13 +9421,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9405,7 +9445,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9420,7 +9460,7 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9428,10 +9468,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9454,18 +9494,20 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>378</v>
+        <v>263</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -9489,13 +9531,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -9513,7 +9555,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9528,18 +9570,18 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9553,7 +9595,7 @@
         <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -9562,18 +9604,20 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9585,7 +9629,7 @@
         <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>21</v>
@@ -9621,7 +9665,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9636,18 +9680,18 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>186</v>
+        <v>379</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9658,32 +9702,30 @@
         <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>246</v>
+        <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>427</v>
+        <v>381</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>428</v>
+        <v>382</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -9695,7 +9737,7 @@
         <v>21</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>21</v>
@@ -9707,13 +9749,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>432</v>
+        <v>21</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -9731,7 +9773,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9746,7 +9788,7 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>433</v>
+        <v>386</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -9754,10 +9796,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9768,7 +9810,7 @@
         <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -9777,16 +9819,16 @@
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>435</v>
+        <v>388</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>436</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>437</v>
+        <v>390</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9837,13 +9879,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -9852,18 +9894,18 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9874,28 +9916,28 @@
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K74" t="s" s="2">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>441</v>
+        <v>395</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>442</v>
+        <v>396</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>443</v>
+        <v>397</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9945,22 +9987,22 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>439</v>
+        <v>398</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>444</v>
+        <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>445</v>
+        <v>399</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>21</v>
@@ -9968,10 +10010,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9991,18 +10033,20 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>100</v>
+        <v>401</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10051,7 +10095,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>102</v>
+        <v>404</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10063,10 +10107,10 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
@@ -10074,21 +10118,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10100,18 +10144,20 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>106</v>
+        <v>263</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>107</v>
+        <v>443</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10135,13 +10181,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -10159,22 +10205,22 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>113</v>
+        <v>442</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>103</v>
+        <v>449</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
@@ -10182,46 +10228,42 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>106</v>
+        <v>451</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10269,7 +10311,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10281,10 +10323,10 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>186</v>
+        <v>454</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
@@ -10292,10 +10334,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10303,10 +10345,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>86</v>
@@ -10318,20 +10360,18 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>246</v>
+        <v>456</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10355,11 +10395,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>458</v>
+        <v>21</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -10377,22 +10419,22 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>237</v>
+        <v>461</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
@@ -10400,10 +10442,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10506,10 +10548,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10579,16 +10621,16 @@
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>113</v>
@@ -10612,47 +10654,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>258</v>
+        <v>466</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>259</v>
+        <v>467</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>260</v>
+        <v>109</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>261</v>
+        <v>468</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10701,7 +10743,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>262</v>
+        <v>469</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10713,21 +10755,21 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>263</v>
+        <v>186</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10735,13 +10777,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
@@ -10750,16 +10792,20 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>99</v>
+        <v>263</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>100</v>
+        <v>471</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -10783,13 +10829,11 @@
         <v>21</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>21</v>
+        <v>475</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -10807,7 +10851,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>102</v>
+        <v>470</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -10819,10 +10863,10 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>21</v>
@@ -10830,21 +10874,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -10856,17 +10900,15 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -10903,31 +10945,31 @@
         <v>21</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>103</v>
@@ -10936,48 +10978,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>268</v>
+        <v>108</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11013,34 +11053,34 @@
         <v>21</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>272</v>
+        <v>113</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>273</v>
+        <v>103</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>21</v>
@@ -11048,10 +11088,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11059,10 +11099,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>86</v>
@@ -11074,7 +11114,7 @@
         <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>275</v>
@@ -11085,7 +11125,9 @@
       <c r="N85" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -11133,13 +11175,13 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
@@ -11148,18 +11190,18 @@
         <v>97</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11167,33 +11209,31 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>282</v>
+        <v>101</v>
       </c>
       <c r="N86" s="2"/>
-      <c r="O86" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
@@ -11241,7 +11281,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>285</v>
+        <v>102</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11253,55 +11293,55 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>288</v>
+        <v>107</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
@@ -11337,45 +11377,45 @@
         <v>21</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>291</v>
+        <v>113</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>292</v>
+        <v>103</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11383,13 +11423,13 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>21</v>
@@ -11398,19 +11438,19 @@
         <v>86</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -11459,7 +11499,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -11474,18 +11514,18 @@
         <v>97</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11499,7 +11539,7 @@
         <v>85</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
@@ -11511,17 +11551,15 @@
         <v>99</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -11569,7 +11607,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -11584,18 +11622,18 @@
         <v>97</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11603,41 +11641,37 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="J90" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K90" t="s" s="2">
-        <v>294</v>
+        <v>161</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>471</v>
+        <v>298</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>474</v>
+        <v>300</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q90" t="s" s="2">
-        <v>475</v>
-      </c>
+      <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
         <v>21</v>
       </c>
@@ -11681,7 +11715,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>470</v>
+        <v>302</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -11690,24 +11724,24 @@
         <v>85</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>477</v>
+        <v>303</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11718,29 +11752,29 @@
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>396</v>
+        <v>99</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>479</v>
+        <v>305</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>480</v>
+        <v>306</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>481</v>
+        <v>307</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -11789,7 +11823,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>478</v>
+        <v>308</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -11804,18 +11838,18 @@
         <v>97</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>482</v>
+        <v>309</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11823,31 +11857,35 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K92" t="s" s="2">
-        <v>484</v>
+        <v>224</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>485</v>
+        <v>311</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>21</v>
       </c>
@@ -11895,10 +11933,10 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>483</v>
+        <v>315</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>85</v>
@@ -11910,7 +11948,7 @@
         <v>97</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>487</v>
+        <v>316</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
@@ -11918,10 +11956,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11941,19 +11979,23 @@
         <v>21</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>100</v>
+        <v>318</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
       </c>
@@ -12001,7 +12043,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>102</v>
+        <v>322</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12013,10 +12055,10 @@
         <v>21</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>103</v>
+        <v>323</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
@@ -12024,48 +12066,52 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>107</v>
+        <v>488</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>108</v>
+        <v>489</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q94" s="2"/>
+      <c r="Q94" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="R94" t="s" s="2">
         <v>21</v>
       </c>
@@ -12097,45 +12143,45 @@
         <v>21</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>113</v>
+        <v>487</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>103</v>
+        <v>494</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12143,33 +12189,33 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>99</v>
+        <v>412</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>319</v>
+        <v>496</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -12217,7 +12263,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>322</v>
+        <v>495</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12226,24 +12272,24 @@
         <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>186</v>
+        <v>499</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12251,32 +12297,30 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>127</v>
+        <v>501</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>325</v>
+        <v>502</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -12301,13 +12345,13 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -12325,10 +12369,10 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>85</v>
@@ -12340,7 +12384,7 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>186</v>
+        <v>504</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>21</v>
@@ -12348,10 +12392,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12371,20 +12415,18 @@
         <v>21</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>332</v>
+        <v>100</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -12433,7 +12475,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>335</v>
+        <v>102</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -12445,10 +12487,10 @@
         <v>21</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>336</v>
+        <v>103</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>21</v>
@@ -12456,21 +12498,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>21</v>
@@ -12479,19 +12521,19 @@
         <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>385</v>
+        <v>107</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>386</v>
+        <v>108</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>387</v>
+        <v>109</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12529,34 +12571,34 @@
         <v>21</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>388</v>
+        <v>113</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>21</v>
@@ -12564,10 +12606,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12575,7 +12617,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>85</v>
@@ -12587,23 +12629,21 @@
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>246</v>
+        <v>99</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>495</v>
+        <v>335</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>496</v>
+        <v>336</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>21</v>
       </c>
@@ -12627,11 +12667,13 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -12649,7 +12691,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>494</v>
+        <v>338</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -12658,13 +12700,13 @@
         <v>85</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>444</v>
+        <v>339</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>500</v>
+        <v>186</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>21</v>
@@ -12672,10 +12714,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12695,18 +12737,20 @@
         <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>100</v>
+        <v>341</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -12731,13 +12775,13 @@
         <v>21</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -12755,7 +12799,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>102</v>
+        <v>346</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -12767,10 +12811,10 @@
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>21</v>
@@ -12778,21 +12822,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>21</v>
@@ -12801,19 +12845,19 @@
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>107</v>
+        <v>348</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>108</v>
+        <v>349</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>109</v>
+        <v>350</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12851,45 +12895,45 @@
         <v>21</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>113</v>
+        <v>351</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>103</v>
+        <v>352</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12897,13 +12941,13 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>21</v>
@@ -12912,20 +12956,18 @@
         <v>86</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>258</v>
+        <v>401</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>259</v>
+        <v>402</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>21</v>
       </c>
@@ -12973,13 +13015,13 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>262</v>
+        <v>404</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>21</v>
@@ -12988,18 +13030,18 @@
         <v>97</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>263</v>
+        <v>186</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13013,7 +13055,7 @@
         <v>85</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>21</v>
@@ -13022,16 +13064,20 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>99</v>
+        <v>263</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>100</v>
+        <v>512</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
       </c>
@@ -13055,13 +13101,11 @@
         <v>21</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -13079,7 +13123,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>102</v>
+        <v>511</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13088,13 +13132,13 @@
         <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>103</v>
+        <v>517</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>21</v>
@@ -13102,21 +13146,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>21</v>
@@ -13128,17 +13172,15 @@
         <v>21</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -13175,31 +13217,31 @@
         <v>21</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>103</v>
@@ -13208,48 +13250,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>268</v>
+        <v>108</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>21</v>
       </c>
@@ -13285,34 +13325,34 @@
         <v>21</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>272</v>
+        <v>113</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>273</v>
+        <v>103</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>21</v>
@@ -13320,10 +13360,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13331,10 +13371,10 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>86</v>
@@ -13346,7 +13386,7 @@
         <v>86</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>275</v>
@@ -13357,7 +13397,9 @@
       <c r="N106" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>21</v>
       </c>
@@ -13405,13 +13447,13 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>21</v>
@@ -13420,18 +13462,18 @@
         <v>97</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13439,33 +13481,31 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>282</v>
+        <v>101</v>
       </c>
       <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>21</v>
       </c>
@@ -13513,7 +13553,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>285</v>
+        <v>102</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -13525,55 +13565,55 @@
         <v>21</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>288</v>
+        <v>107</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
@@ -13609,45 +13649,45 @@
         <v>21</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>291</v>
+        <v>113</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>292</v>
+        <v>103</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13655,13 +13695,13 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>21</v>
@@ -13670,19 +13710,19 @@
         <v>86</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -13731,7 +13771,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -13746,18 +13786,18 @@
         <v>97</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13771,7 +13811,7 @@
         <v>85</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>21</v>
@@ -13783,17 +13823,15 @@
         <v>99</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>21</v>
       </c>
@@ -13841,7 +13879,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -13856,14 +13894,450 @@
         <v>97</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL110" t="s" s="2">
+      <c r="P112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL114" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL110">
+  <autoFilter ref="A1:AL114">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13873,7 +14347,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI109">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1605,7 +1605,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown | unavailable] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein | unavailable: Plan ist leer weil alle Einträge entfernt wurden</t>
+    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown ] Bedeutung: notstarted: Intitalzustand - noch nie befüllt; nilknown: Der Plan wurde vom GDA explizit als leer dokumentiert oder alle Einträge wurden abgesetzt, storniert oder gelöscht.</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3917" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3917" uniqueCount="527">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1004,7 +1004,7 @@
     <t>List.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1124,9 +1124,6 @@
     <t>List.subject.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
     <t>The purpose of this identifier.</t>
   </si>
   <si>
@@ -1389,9 +1386,6 @@
   </si>
   <si>
     <t>List.orderedBy</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -6562,7 +6556,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -7534,7 +7528,7 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7549,16 +7543,16 @@
         <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7586,28 +7580,28 @@
         <v>182</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7622,7 +7616,7 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7630,10 +7624,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7659,16 +7653,16 @@
         <v>263</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7696,28 +7690,28 @@
         <v>143</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z53" t="s" s="2">
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7732,7 +7726,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7740,10 +7734,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7769,16 +7763,16 @@
         <v>127</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -7791,43 +7785,43 @@
         <v>21</v>
       </c>
       <c r="T54" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7842,7 +7836,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7850,10 +7844,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7879,13 +7873,13 @@
         <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7899,43 +7893,43 @@
         <v>21</v>
       </c>
       <c r="T55" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7950,7 +7944,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
@@ -7958,10 +7952,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7984,13 +7978,13 @@
         <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8041,7 +8035,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8056,7 +8050,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -8064,10 +8058,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8090,16 +8084,16 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8149,7 +8143,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8164,7 +8158,7 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
@@ -8172,10 +8166,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8201,13 +8195,13 @@
         <v>99</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8257,7 +8251,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8280,10 +8274,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8306,13 +8300,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8363,7 +8357,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8378,18 +8372,18 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8412,19 +8406,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8473,7 +8467,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8488,22 +8482,22 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8522,19 +8516,19 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8583,7 +8577,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8598,18 +8592,18 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>427</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8712,10 +8706,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8820,10 +8814,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8928,10 +8922,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9036,10 +9030,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9144,10 +9138,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9250,10 +9244,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9358,10 +9352,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9372,7 +9366,7 @@
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9387,16 +9381,16 @@
         <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9424,28 +9418,28 @@
         <v>182</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9460,7 +9454,7 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9468,10 +9462,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9497,16 +9491,16 @@
         <v>263</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -9534,28 +9528,28 @@
         <v>143</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9570,7 +9564,7 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
@@ -9578,10 +9572,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9607,16 +9601,16 @@
         <v>127</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9629,43 +9623,43 @@
         <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9680,7 +9674,7 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
@@ -9688,10 +9682,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9717,13 +9711,13 @@
         <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9737,43 +9731,43 @@
         <v>21</v>
       </c>
       <c r="T72" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9788,7 +9782,7 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -9796,10 +9790,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9822,13 +9816,13 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9879,7 +9873,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9894,7 +9888,7 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
@@ -9902,10 +9896,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9928,16 +9922,16 @@
         <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9987,7 +9981,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10002,7 +9996,7 @@
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>21</v>
@@ -10010,10 +10004,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10039,13 +10033,13 @@
         <v>99</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10095,7 +10089,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10118,10 +10112,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10147,16 +10141,16 @@
         <v>263</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10184,10 +10178,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -10205,7 +10199,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10220,7 +10214,7 @@
         <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
@@ -10228,10 +10222,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10254,13 +10248,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10311,7 +10305,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10326,7 +10320,7 @@
         <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
@@ -10334,10 +10328,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10360,16 +10354,16 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10419,7 +10413,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10428,13 +10422,13 @@
         <v>78</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
@@ -10442,10 +10436,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10548,10 +10542,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10656,14 +10650,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10685,16 +10679,16 @@
         <v>106</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10743,7 +10737,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10766,10 +10760,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10795,16 +10789,16 @@
         <v>263</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -10833,7 +10827,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -10851,7 +10845,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -10874,10 +10868,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10980,10 +10974,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11088,10 +11082,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11102,7 +11096,7 @@
         <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>86</v>
@@ -11198,10 +11192,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11304,10 +11298,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11412,10 +11406,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11522,10 +11516,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11630,10 +11624,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11738,10 +11732,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11846,10 +11840,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11956,10 +11950,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11970,7 +11964,7 @@
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>21</v>
@@ -12066,10 +12060,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12095,82 +12089,82 @@
         <v>224</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="O94" t="s" s="2">
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI94" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q94" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="R94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
@@ -12178,10 +12172,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12204,17 +12198,17 @@
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -12263,7 +12257,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12278,7 +12272,7 @@
         <v>97</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>21</v>
@@ -12286,10 +12280,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12312,13 +12306,13 @@
         <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12369,7 +12363,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>85</v>
@@ -12384,7 +12378,7 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>21</v>
@@ -12392,10 +12386,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12498,10 +12492,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12606,10 +12600,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12714,10 +12708,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12822,10 +12816,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12930,10 +12924,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12959,13 +12953,13 @@
         <v>99</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13015,7 +13009,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13038,10 +13032,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13067,16 +13061,16 @@
         <v>263</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -13105,7 +13099,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -13123,7 +13117,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13132,13 +13126,13 @@
         <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>21</v>
@@ -13146,10 +13140,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13252,10 +13246,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13360,10 +13354,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13374,7 +13368,7 @@
         <v>85</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>86</v>
@@ -13470,10 +13464,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13576,10 +13570,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13684,10 +13678,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13794,10 +13788,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13902,10 +13896,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14010,10 +14004,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14118,10 +14112,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14228,10 +14222,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14242,7 +14236,7 @@
         <v>77</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,11 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Der Medikationsplan wird durch eine List-Ressource abgebildet und enthält:
-- 0..* Einträge (List.entry). 
-Jedes List.entry.item enhält genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest).
-Die Reihung der List.entries bestimmt die Reihenfolge der Medikationsplaneinträge. 
-Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
+    <t>Profil für einen Medikationsplan.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1413,7 +1409,7 @@
 </t>
   </si>
   <si>
-    <t>Fachliche Begrüundung: Auf dieser Ebene keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests(Planeinträgen möglich)</t>
+    <t>Fachliche Begründung: Auf dieser Ebene keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests(Planeinträgen möglich)</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1021,7 +1021,7 @@
     <t>List.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-patient)
 </t>
   </si>
   <si>
@@ -1317,7 +1317,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung)
 </t>
   </si>
   <si>
@@ -1981,7 +1981,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="201.5546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="205.203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3917" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3917" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -759,7 +759,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplans. Fixer Wert: current</t>
+    <t>Status des Medikationsplans. Fixer Wert: current.</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -838,7 +838,7 @@
 </t>
   </si>
   <si>
-    <t>Code der den Medikationsplan identifiziert</t>
+    <t>Code, der den Medikationsplan identifiziert.</t>
   </si>
   <si>
     <t>This code defines the purpose of the list - why it was created.</t>
@@ -1000,7 +1000,7 @@
     <t>List.code.text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1120,6 +1120,9 @@
     <t>List.subject.identifier.use</t>
   </si>
   <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
     <t>The purpose of this identifier.</t>
   </si>
   <si>
@@ -1384,6 +1387,9 @@
     <t>List.orderedBy</t>
   </si>
   <si>
+    <t>What order the list has</t>
+  </si>
+  <si>
     <t>What order applies to the items in the list.</t>
   </si>
   <si>
@@ -1409,7 +1415,7 @@
 </t>
   </si>
   <si>
-    <t>Fachliche Begründung: Auf dieser Ebene keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests(Planeinträgen möglich)</t>
+    <t>Fachliche Begründung: Auf dieser Ebene existieren keine Freitext-Anmerkungen im Medikationsplan. Freitext ist in den jeweiligen MedicationRequests (Planeinträgen möglich).</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -1470,7 +1476,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Planeintrag wird hinzugefügt | Unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Planeintrag wird geändert | Removed: Bestehender Planeintrag wird entfernt</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [new | unchanged | changed | removed]. Bedeutung: new: Neuer Planeintrag wird hinzugefügt | unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | changed: Bestehender Planeintrag wird geändert | removed: Bestehender Planeintrag wird entfernt</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -1546,7 +1552,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Fachliche Begründung: Das Datum der initialen Aufnahme eines Eintrags wird nicht auf Ebene der Liste dokumentiert. Datumsinformationen werden im referenzierten Medikationsplaneintrag dokumentiert.</t>
+    <t>Fachliche Begründung: Das Datum der initialen Aufnahme eines Eintrags wird nicht auf Ebene der Liste, sondern im referenzierten Medikationsplaneintrag dokumentiert.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -1595,7 +1601,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown ] Bedeutung: notstarted: Intitalzustand - noch nie befüllt; nilknown: Der Plan wurde vom GDA explizit als leer dokumentiert oder alle Einträge wurden abgesetzt, storniert oder gelöscht.</t>
+    <t>Begründung, welshalb der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown ] Bedeutung: notstarted: Intitalzustand - noch nie befüllt; nilknown: Der Plan wurde vom GDA explizit als leer dokumentiert oder alle Einträge wurden abgesetzt, storniert oder gelöscht.</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -7539,16 +7545,16 @@
         <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7576,10 +7582,10 @@
         <v>182</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7597,7 +7603,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7612,7 +7618,7 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7620,10 +7626,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7649,16 +7655,16 @@
         <v>263</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7686,10 +7692,10 @@
         <v>143</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7707,7 +7713,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7722,7 +7728,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7730,10 +7736,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7759,16 +7765,16 @@
         <v>127</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -7781,7 +7787,7 @@
         <v>21</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>21</v>
@@ -7817,7 +7823,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7832,7 +7838,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7840,10 +7846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7869,13 +7875,13 @@
         <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7889,7 +7895,7 @@
         <v>21</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>21</v>
@@ -7925,7 +7931,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7940,7 +7946,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
@@ -7948,10 +7954,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7974,13 +7980,13 @@
         <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8031,7 +8037,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8046,7 +8052,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -8054,10 +8060,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8080,16 +8086,16 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8139,7 +8145,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8154,7 +8160,7 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
@@ -8162,10 +8168,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8191,13 +8197,13 @@
         <v>99</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8247,7 +8253,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8270,10 +8276,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8296,13 +8302,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8353,7 +8359,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8368,18 +8374,18 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8402,19 +8408,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8463,7 +8469,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8478,22 +8484,22 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8512,19 +8518,19 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8573,7 +8579,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8588,18 +8594,18 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8702,10 +8708,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8810,10 +8816,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8918,10 +8924,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9026,10 +9032,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9134,10 +9140,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9240,10 +9246,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9348,10 +9354,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9377,16 +9383,16 @@
         <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9414,10 +9420,10 @@
         <v>182</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9435,7 +9441,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9450,7 +9456,7 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9458,10 +9464,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9487,16 +9493,16 @@
         <v>263</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -9524,10 +9530,10 @@
         <v>143</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -9545,7 +9551,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9560,7 +9566,7 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
@@ -9568,10 +9574,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9597,16 +9603,16 @@
         <v>127</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9619,7 +9625,7 @@
         <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>21</v>
@@ -9655,7 +9661,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9670,7 +9676,7 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
@@ -9678,10 +9684,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9707,13 +9713,13 @@
         <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9727,7 +9733,7 @@
         <v>21</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>21</v>
@@ -9763,7 +9769,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9778,7 +9784,7 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -9786,10 +9792,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9812,13 +9818,13 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9869,7 +9875,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9884,7 +9890,7 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
@@ -9892,10 +9898,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9918,16 +9924,16 @@
         <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9977,7 +9983,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -9992,7 +9998,7 @@
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>21</v>
@@ -10000,10 +10006,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10029,13 +10035,13 @@
         <v>99</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10085,7 +10091,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10108,10 +10114,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10137,16 +10143,16 @@
         <v>263</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>318</v>
+        <v>443</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10174,10 +10180,10 @@
         <v>165</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -10195,7 +10201,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10210,7 +10216,7 @@
         <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
@@ -10218,10 +10224,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10244,13 +10250,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10301,7 +10307,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10316,7 +10322,7 @@
         <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
@@ -10324,10 +10330,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10350,16 +10356,16 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10409,7 +10415,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10418,13 +10424,13 @@
         <v>78</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
@@ -10432,10 +10438,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10538,10 +10544,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10646,14 +10652,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10675,16 +10681,16 @@
         <v>106</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10733,7 +10739,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10756,10 +10762,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10785,16 +10791,16 @@
         <v>263</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -10823,7 +10829,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -10841,7 +10847,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -10864,10 +10870,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10970,10 +10976,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11078,10 +11084,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11188,10 +11194,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11294,10 +11300,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11402,10 +11408,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11512,10 +11518,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11620,10 +11626,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11728,10 +11734,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11836,10 +11842,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11946,10 +11952,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12056,10 +12062,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12085,68 +12091,68 @@
         <v>224</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q94" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="R94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
       </c>
@@ -12154,13 +12160,13 @@
         <v>85</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
@@ -12168,10 +12174,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12194,17 +12200,17 @@
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -12253,7 +12259,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12268,7 +12274,7 @@
         <v>97</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>21</v>
@@ -12276,10 +12282,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12302,13 +12308,13 @@
         <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12359,7 +12365,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>85</v>
@@ -12374,7 +12380,7 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>21</v>
@@ -12382,10 +12388,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12488,10 +12494,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12596,10 +12602,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12704,10 +12710,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12812,10 +12818,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12920,10 +12926,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12949,13 +12955,13 @@
         <v>99</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13005,7 +13011,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13028,10 +13034,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13057,16 +13063,16 @@
         <v>263</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -13095,7 +13101,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -13113,7 +13119,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13122,13 +13128,13 @@
         <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>21</v>
@@ -13136,10 +13142,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13242,10 +13248,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13350,10 +13356,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13460,10 +13466,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13566,10 +13572,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13674,10 +13680,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13784,10 +13790,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13892,10 +13898,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14000,10 +14006,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14108,10 +14114,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14218,10 +14224,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$110</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3917" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="513">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,307 +676,259 @@
 </t>
   </si>
   <si>
-    <t>List.extension:PatientModified.id</t>
-  </si>
-  <si>
-    <t>List.extension.id</t>
-  </si>
-  <si>
-    <t>List.extension:PatientModified.extension</t>
-  </si>
-  <si>
-    <t>List.extension.extension</t>
-  </si>
-  <si>
-    <t>List.extension:PatientModified.url</t>
-  </si>
-  <si>
-    <t>List.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-patient-modified</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>List.extension:PatientModified.value[x]</t>
-  </si>
-  <si>
-    <t>List.extension.value[x]</t>
+    <t>List.modifierExtension</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>List.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business identifier</t>
+  </si>
+  <si>
+    <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>List.status</t>
+  </si>
+  <si>
+    <t>Status des Medikationsplans. Fixer Wert: current.</t>
+  </si>
+  <si>
+    <t>Indicates the current state of this list.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>current</t>
+  </si>
+  <si>
+    <t>The current state of the list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-status|4.0.1</t>
+  </si>
+  <si>
+    <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>List.mode</t>
+  </si>
+  <si>
+    <t>Der Medikationsplan ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
+  </si>
+  <si>
+    <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
+  </si>
+  <si>
+    <t>Lists are used in various ways, and it must be known in what way it is safe to use them.</t>
+  </si>
+  <si>
+    <t>working</t>
+  </si>
+  <si>
+    <t>The processing mode that applies to this list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>List.title</t>
+  </si>
+  <si>
+    <t>Descriptive name for the list</t>
+  </si>
+  <si>
+    <t>A label for the list assigned by the author.</t>
+  </si>
+  <si>
+    <t>Allows customization beyond just the code identifying the kind of list.</t>
+  </si>
+  <si>
+    <t>Dr. Jane's Patients</t>
+  </si>
+  <si>
+    <t>.title</t>
+  </si>
+  <si>
+    <t>List.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Code, der den Medikationsplan identifiziert.</t>
+  </si>
+  <si>
+    <t>This code defines the purpose of the list - why it was created.</t>
+  </si>
+  <si>
+    <t>If there is no code, the purpose of the list is implied where it is used, such as in a document section using Document.section.code.</t>
+  </si>
+  <si>
+    <t>Lists often contain subsets of resources rather than an exhaustive list.  The code identifies what type of subset is included.</t>
+  </si>
+  <si>
+    <t>What the purpose of a list is.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-example-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>List.code.id</t>
+  </si>
+  <si>
+    <t>List.code.extension</t>
+  </si>
+  <si>
+    <t>List.code.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>List.code.coding.id</t>
+  </si>
+  <si>
+    <t>List.code.coding.extension</t>
+  </si>
+  <si>
+    <t>List.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>List.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>List.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>736378000</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>List.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>List.code.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>List.modifierExtension</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>List.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business identifier</t>
-  </si>
-  <si>
-    <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>List.status</t>
-  </si>
-  <si>
-    <t>Status des Medikationsplans. Fixer Wert: current.</t>
-  </si>
-  <si>
-    <t>Indicates the current state of this list.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>current</t>
-  </si>
-  <si>
-    <t>The current state of the list.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-status|4.0.1</t>
-  </si>
-  <si>
-    <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>List.mode</t>
-  </si>
-  <si>
-    <t>Der Medikationsplan ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
-  </si>
-  <si>
-    <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because a change list must not be misunderstood as a complete list.</t>
-  </si>
-  <si>
-    <t>Lists are used in various ways, and it must be known in what way it is safe to use them.</t>
-  </si>
-  <si>
-    <t>working</t>
-  </si>
-  <si>
-    <t>The processing mode that applies to this list.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>List.title</t>
-  </si>
-  <si>
-    <t>Descriptive name for the list</t>
-  </si>
-  <si>
-    <t>A label for the list assigned by the author.</t>
-  </si>
-  <si>
-    <t>Allows customization beyond just the code identifying the kind of list.</t>
-  </si>
-  <si>
-    <t>Dr. Jane's Patients</t>
-  </si>
-  <si>
-    <t>.title</t>
-  </si>
-  <si>
-    <t>List.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Code, der den Medikationsplan identifiziert.</t>
-  </si>
-  <si>
-    <t>This code defines the purpose of the list - why it was created.</t>
-  </si>
-  <si>
-    <t>If there is no code, the purpose of the list is implied where it is used, such as in a document section using Document.section.code.</t>
-  </si>
-  <si>
-    <t>Lists often contain subsets of resources rather than an exhaustive list.  The code identifies what type of subset is included.</t>
-  </si>
-  <si>
-    <t>What the purpose of a list is.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-example-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>List.code.id</t>
-  </si>
-  <si>
-    <t>List.code.extension</t>
-  </si>
-  <si>
-    <t>List.code.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>List.code.coding.id</t>
-  </si>
-  <si>
-    <t>List.code.coding.extension</t>
-  </si>
-  <si>
-    <t>List.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>List.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>List.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>736378000</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>List.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>List.code.coding.userSelected</t>
   </si>
   <si>
     <t>If this coding was chosen directly by the user</t>
@@ -1974,10 +1926,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL114"/>
+  <dimension ref="A1:AL110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.80078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="31.48046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="31.48046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.14453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -4391,7 +4343,7 @@
         <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4402,25 +4354,25 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>100</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4471,22 +4423,22 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -4494,7 +4446,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>214</v>
@@ -4508,7 +4460,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4520,13 +4472,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>106</v>
+        <v>215</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4565,19 +4517,19 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>113</v>
+        <v>214</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4589,21 +4541,21 @@
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4620,22 +4572,22 @@
         <v>86</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4643,50 +4595,50 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="S25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>221</v>
-      </c>
       <c r="AG25" t="s" s="2">
         <v>85</v>
       </c>
@@ -4697,21 +4649,21 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4728,28 +4680,32 @@
         <v>86</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>224</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>21</v>
@@ -4767,13 +4723,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4791,10 +4747,10 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>85</v>
@@ -4806,18 +4762,18 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4828,28 +4784,30 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="J27" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4861,7 +4819,7 @@
         <v>21</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>21</v>
@@ -4897,33 +4855,33 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4931,31 +4889,35 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4979,13 +4941,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5003,13 +4965,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -5018,18 +4980,18 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5037,32 +4999,30 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>238</v>
+        <v>100</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5072,7 +5032,7 @@
         <v>21</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>21</v>
@@ -5087,13 +5047,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5111,10 +5071,10 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>102</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>85</v>
@@ -5123,63 +5083,61 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>244</v>
+        <v>103</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>108</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>21</v>
@@ -5197,57 +5155,57 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>113</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>254</v>
+        <v>103</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5255,13 +5213,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5270,17 +5228,19 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5293,7 +5253,7 @@
         <v>21</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>21</v>
@@ -5329,13 +5289,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5344,18 +5304,18 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5363,35 +5323,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>263</v>
+        <v>99</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5415,13 +5371,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5439,7 +5395,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>262</v>
+        <v>102</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5451,32 +5407,32 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>103</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5488,15 +5444,17 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5533,31 +5491,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>103</v>
@@ -5566,46 +5524,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5614,7 +5574,7 @@
         <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -5641,34 +5601,34 @@
         <v>21</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>103</v>
+        <v>273</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
@@ -5687,7 +5647,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>85</v>
@@ -5702,7 +5662,7 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>275</v>
@@ -5713,9 +5673,7 @@
       <c r="N35" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O35" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5763,13 +5721,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -5778,18 +5736,18 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5797,37 +5755,39 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>21</v>
@@ -5869,7 +5829,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5881,55 +5841,55 @@
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5965,45 +5925,45 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>113</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6011,13 +5971,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6026,19 +5986,19 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6048,7 +6008,7 @@
         <v>21</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>21</v>
@@ -6087,7 +6047,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6102,18 +6062,18 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6124,10 +6084,10 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6139,15 +6099,17 @@
         <v>99</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6195,7 +6157,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6210,7 +6172,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -6218,10 +6180,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6244,24 +6206,26 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
@@ -6303,7 +6267,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6318,18 +6282,18 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6343,27 +6307,25 @@
         <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>305</v>
+        <v>100</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>306</v>
+        <v>101</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>307</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6411,7 +6373,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>102</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6423,10 +6385,10 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>309</v>
+        <v>103</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6434,21 +6396,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6457,23 +6419,21 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>107</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6509,45 +6469,45 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>113</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>103</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6558,10 +6518,10 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6573,17 +6533,15 @@
         <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O43" t="s" s="2">
         <v>321</v>
       </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6640,13 +6598,13 @@
         <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>323</v>
+        <v>186</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6665,7 +6623,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>85</v>
@@ -6680,20 +6638,18 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6717,13 +6673,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6741,7 +6697,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6756,18 +6712,18 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>330</v>
+        <v>186</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>331</v>
       </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6781,24 +6737,26 @@
         <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>99</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6847,7 +6805,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>102</v>
+        <v>335</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6859,10 +6817,10 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6870,21 +6828,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6896,17 +6854,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6943,31 +6899,31 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>103</v>
@@ -6976,44 +6932,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>107</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
+        <v>108</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>337</v>
+        <v>109</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7051,45 +7007,45 @@
         <v>21</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>338</v>
+        <v>113</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7100,30 +7056,32 @@
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7147,7 +7105,7 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="Y48" t="s" s="2">
         <v>344</v>
@@ -7186,18 +7144,18 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>186</v>
+        <v>347</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7211,7 +7169,7 @@
         <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7220,18 +7178,20 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7255,13 +7215,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7279,7 +7239,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7294,18 +7254,18 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7319,25 +7279,29 @@
         <v>85</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>100</v>
+        <v>357</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7349,7 +7313,7 @@
         <v>21</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>21</v>
@@ -7385,7 +7349,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>102</v>
+        <v>362</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7397,53 +7361,53 @@
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>103</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>107</v>
+        <v>365</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>108</v>
+        <v>366</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>109</v>
+        <v>367</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7457,7 +7421,7 @@
         <v>21</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>21</v>
@@ -7481,34 +7445,34 @@
         <v>21</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>113</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>103</v>
+        <v>370</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7516,10 +7480,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7530,32 +7494,28 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>161</v>
+        <v>372</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7579,13 +7539,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7603,7 +7563,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7618,7 +7578,7 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7626,10 +7586,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7652,20 +7612,18 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>263</v>
+        <v>378</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7689,13 +7647,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7713,7 +7671,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7728,18 +7686,18 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7753,7 +7711,7 @@
         <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -7762,20 +7720,18 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7787,7 +7743,7 @@
         <v>21</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>21</v>
@@ -7823,7 +7779,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7838,18 +7794,18 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>379</v>
+        <v>186</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7860,29 +7816,27 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>99</v>
+        <v>390</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7895,7 +7849,7 @@
         <v>21</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>21</v>
@@ -7931,7 +7885,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7946,18 +7900,18 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7971,7 +7925,7 @@
         <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -7980,16 +7934,20 @@
         <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8037,7 +7995,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8052,32 +8010,32 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8086,18 +8044,20 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8145,7 +8105,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8160,18 +8120,18 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8191,20 +8151,18 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>401</v>
+        <v>100</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8253,7 +8211,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>404</v>
+        <v>102</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8265,10 +8223,10 @@
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
@@ -8276,21 +8234,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8302,15 +8260,17 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>406</v>
+        <v>106</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>407</v>
+        <v>107</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8347,45 +8307,45 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>405</v>
+        <v>113</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>409</v>
+        <v>103</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8408,20 +8368,18 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>412</v>
+        <v>99</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>413</v>
+        <v>319</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>414</v>
+        <v>320</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8469,7 +8427,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8478,32 +8436,32 @@
         <v>85</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>417</v>
+        <v>186</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>85</v>
@@ -8518,20 +8476,18 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>421</v>
+        <v>127</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>422</v>
+        <v>325</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>423</v>
+        <v>326</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8555,13 +8511,13 @@
         <v>21</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>21</v>
@@ -8579,7 +8535,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>419</v>
+        <v>330</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8594,18 +8550,18 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>426</v>
+        <v>186</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>427</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8619,24 +8575,26 @@
         <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>99</v>
+        <v>215</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8685,7 +8643,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>102</v>
+        <v>335</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8697,10 +8655,10 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>21</v>
@@ -8708,21 +8666,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -8734,17 +8692,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -8781,31 +8737,31 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>103</v>
@@ -8814,44 +8770,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>335</v>
+        <v>107</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>336</v>
+        <v>108</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>337</v>
+        <v>109</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8889,45 +8845,45 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>338</v>
+        <v>113</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8938,30 +8894,32 @@
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -8985,7 +8943,7 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="Y65" t="s" s="2">
         <v>344</v>
@@ -9024,18 +8982,18 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>186</v>
+        <v>347</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9049,7 +9007,7 @@
         <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9058,18 +9016,20 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9093,13 +9053,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9117,7 +9077,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9132,18 +9092,18 @@
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9157,25 +9117,29 @@
         <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>100</v>
+        <v>357</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9187,7 +9151,7 @@
         <v>21</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>21</v>
@@ -9223,7 +9187,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>102</v>
+        <v>362</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9235,53 +9199,53 @@
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>103</v>
+        <v>363</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>107</v>
+        <v>365</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>108</v>
+        <v>366</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>109</v>
+        <v>367</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9295,7 +9259,7 @@
         <v>21</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>21</v>
@@ -9319,34 +9283,34 @@
         <v>21</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>113</v>
+        <v>369</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>103</v>
+        <v>370</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
@@ -9354,10 +9318,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9368,32 +9332,28 @@
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>372</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9417,13 +9377,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9441,7 +9401,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9456,7 +9416,7 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>21</v>
@@ -9464,10 +9424,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9490,20 +9450,18 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>263</v>
+        <v>378</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -9527,13 +9485,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -9551,7 +9509,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9566,18 +9524,18 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9591,7 +9549,7 @@
         <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -9600,20 +9558,18 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9625,7 +9581,7 @@
         <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>21</v>
@@ -9661,7 +9617,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9676,18 +9632,18 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>379</v>
+        <v>186</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9698,30 +9654,32 @@
         <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>99</v>
+        <v>246</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -9733,7 +9691,7 @@
         <v>21</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>21</v>
@@ -9745,13 +9703,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -9769,7 +9727,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9784,7 +9742,7 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
@@ -9792,10 +9750,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9806,7 +9764,7 @@
         <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -9815,16 +9773,16 @@
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>388</v>
+        <v>435</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>389</v>
+        <v>436</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>390</v>
+        <v>437</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9875,13 +9833,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -9890,18 +9848,18 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>392</v>
+        <v>438</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9912,28 +9870,28 @@
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9983,22 +9941,22 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>21</v>
@@ -10006,10 +9964,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10029,20 +9987,18 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>401</v>
+        <v>100</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10091,7 +10047,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>404</v>
+        <v>102</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10103,10 +10059,10 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
@@ -10114,21 +10070,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10140,20 +10096,18 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>263</v>
+        <v>106</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>443</v>
+        <v>107</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>444</v>
+        <v>108</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10177,13 +10131,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -10201,22 +10155,22 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>113</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>449</v>
+        <v>103</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
@@ -10224,42 +10178,46 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="N77" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10307,7 +10265,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10319,10 +10277,10 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>454</v>
+        <v>186</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
@@ -10330,10 +10288,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10341,10 +10299,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>86</v>
@@ -10356,18 +10314,20 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10391,13 +10351,11 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>21</v>
+        <v>459</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -10415,22 +10373,22 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>461</v>
+        <v>237</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
@@ -10438,10 +10396,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10544,10 +10502,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10617,16 +10575,16 @@
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>113</v>
@@ -10650,47 +10608,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>465</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>258</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>259</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>109</v>
+        <v>260</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>468</v>
+        <v>261</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10739,7 +10697,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>469</v>
+        <v>262</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10751,21 +10709,21 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10773,13 +10731,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
@@ -10788,20 +10746,16 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>263</v>
+        <v>99</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>471</v>
+        <v>100</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
       </c>
@@ -10825,11 +10779,13 @@
         <v>21</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -10847,7 +10803,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>470</v>
+        <v>102</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -10859,10 +10815,10 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>254</v>
+        <v>103</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>21</v>
@@ -10870,21 +10826,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -10896,15 +10852,17 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -10941,31 +10899,31 @@
         <v>21</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>103</v>
@@ -10974,46 +10932,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11049,34 +11009,34 @@
         <v>21</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>103</v>
+        <v>273</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>21</v>
@@ -11084,10 +11044,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11095,7 +11055,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>85</v>
@@ -11110,7 +11070,7 @@
         <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>275</v>
@@ -11121,9 +11081,7 @@
       <c r="N85" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O85" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -11171,13 +11129,13 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
@@ -11186,18 +11144,18 @@
         <v>97</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11205,31 +11163,33 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
@@ -11277,7 +11237,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11289,55 +11249,55 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
@@ -11373,45 +11333,45 @@
         <v>21</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>113</v>
+        <v>291</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11419,13 +11379,13 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>21</v>
@@ -11434,19 +11394,19 @@
         <v>86</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -11495,7 +11455,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -11510,18 +11470,18 @@
         <v>97</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11532,10 +11492,10 @@
         <v>77</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
@@ -11547,15 +11507,17 @@
         <v>99</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -11603,7 +11565,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -11618,18 +11580,18 @@
         <v>97</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11637,37 +11599,41 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I90" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I90" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J90" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>161</v>
+        <v>294</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>298</v>
+        <v>472</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O90" t="s" s="2">
-        <v>300</v>
+        <v>475</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="R90" t="s" s="2">
         <v>21</v>
       </c>
@@ -11711,7 +11677,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>302</v>
+        <v>471</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -11720,24 +11686,24 @@
         <v>85</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>303</v>
+        <v>478</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11748,29 +11714,29 @@
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>99</v>
+        <v>396</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>305</v>
+        <v>480</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>306</v>
+        <v>481</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>307</v>
+        <v>482</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -11819,7 +11785,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>308</v>
+        <v>479</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -11834,18 +11800,18 @@
         <v>97</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>309</v>
+        <v>483</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11853,35 +11819,31 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>224</v>
+        <v>485</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>311</v>
+        <v>486</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
       </c>
@@ -11929,10 +11891,10 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>315</v>
+        <v>484</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>85</v>
@@ -11944,7 +11906,7 @@
         <v>97</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>316</v>
+        <v>488</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
@@ -11952,10 +11914,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11966,7 +11928,7 @@
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>21</v>
@@ -11975,23 +11937,19 @@
         <v>21</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>318</v>
+        <v>100</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
       </c>
@@ -12039,7 +11997,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>322</v>
+        <v>102</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12051,10 +12009,10 @@
         <v>21</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>323</v>
+        <v>103</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
@@ -12062,122 +12020,118 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>488</v>
+        <v>107</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>489</v>
+        <v>108</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O94" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="P94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q94" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="R94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="B95" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12185,33 +12139,33 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>412</v>
+        <v>99</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>496</v>
+        <v>319</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -12259,7 +12213,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>495</v>
+        <v>322</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12268,24 +12222,24 @@
         <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>499</v>
+        <v>186</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12293,30 +12247,32 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K96" t="s" s="2">
-        <v>501</v>
+        <v>127</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>502</v>
+        <v>325</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -12341,13 +12297,13 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -12365,10 +12321,10 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>85</v>
@@ -12380,7 +12336,7 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>504</v>
+        <v>186</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>21</v>
@@ -12388,10 +12344,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12411,18 +12367,20 @@
         <v>21</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>99</v>
+        <v>215</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -12471,7 +12429,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>102</v>
+        <v>335</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -12483,10 +12441,10 @@
         <v>21</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>21</v>
@@ -12494,21 +12452,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>21</v>
@@ -12517,19 +12475,19 @@
         <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>107</v>
+        <v>385</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>108</v>
+        <v>386</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>109</v>
+        <v>387</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12567,34 +12525,34 @@
         <v>21</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>113</v>
+        <v>388</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>21</v>
@@ -12602,10 +12560,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12613,7 +12571,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>85</v>
@@ -12625,21 +12583,23 @@
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>99</v>
+        <v>246</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>335</v>
+        <v>496</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>336</v>
+        <v>497</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
       </c>
@@ -12663,13 +12623,11 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -12687,7 +12645,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>338</v>
+        <v>495</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -12696,13 +12654,13 @@
         <v>85</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>339</v>
+        <v>444</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>186</v>
+        <v>501</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>21</v>
@@ -12710,10 +12668,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12733,20 +12691,18 @@
         <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>341</v>
+        <v>100</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -12771,13 +12727,13 @@
         <v>21</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -12795,7 +12751,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -12807,10 +12763,10 @@
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>21</v>
@@ -12818,21 +12774,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>21</v>
@@ -12841,19 +12797,19 @@
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>348</v>
+        <v>107</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>350</v>
+        <v>109</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12891,45 +12847,45 @@
         <v>21</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>351</v>
+        <v>113</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>352</v>
+        <v>103</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12937,13 +12893,13 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>21</v>
@@ -12952,18 +12908,20 @@
         <v>86</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>401</v>
+        <v>258</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>402</v>
+        <v>259</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
       </c>
@@ -13011,13 +12969,13 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>404</v>
+        <v>262</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>21</v>
@@ -13026,18 +12984,18 @@
         <v>97</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13051,7 +13009,7 @@
         <v>85</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>21</v>
@@ -13060,20 +13018,16 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>263</v>
+        <v>99</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>512</v>
+        <v>100</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>21</v>
       </c>
@@ -13097,11 +13051,13 @@
         <v>21</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>516</v>
+        <v>21</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -13119,7 +13075,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>511</v>
+        <v>102</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13128,13 +13084,13 @@
         <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>517</v>
+        <v>103</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>21</v>
@@ -13142,21 +13098,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>21</v>
@@ -13168,15 +13124,17 @@
         <v>21</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -13213,31 +13171,31 @@
         <v>21</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>103</v>
@@ -13246,46 +13204,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
       </c>
@@ -13321,34 +13281,34 @@
         <v>21</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>113</v>
+        <v>272</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>103</v>
+        <v>273</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>21</v>
@@ -13356,10 +13316,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13367,7 +13327,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>85</v>
@@ -13382,7 +13342,7 @@
         <v>86</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>275</v>
@@ -13393,9 +13353,7 @@
       <c r="N106" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O106" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>21</v>
       </c>
@@ -13443,13 +13401,13 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>21</v>
@@ -13458,18 +13416,18 @@
         <v>97</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13477,31 +13435,33 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
       </c>
@@ -13549,7 +13509,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -13561,55 +13521,55 @@
         <v>21</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
@@ -13645,45 +13605,45 @@
         <v>21</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>113</v>
+        <v>291</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13691,13 +13651,13 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>21</v>
@@ -13706,19 +13666,19 @@
         <v>86</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -13767,7 +13727,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -13782,18 +13742,18 @@
         <v>97</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13804,10 +13764,10 @@
         <v>77</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>21</v>
@@ -13819,15 +13779,17 @@
         <v>99</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>21</v>
       </c>
@@ -13875,7 +13837,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -13890,450 +13852,14 @@
         <v>97</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AL114" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL114">
+  <autoFilter ref="A1:AL110">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14343,7 +13869,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI109">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -267,7 +267,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}at-emed-list-same-patient:Alle in der Liste referenzierten Patienten müssen gleich sein {subject.resolve() = entry.item.resolve().ofType(MedicationRequest).subject.resolve()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}at-emed-list-same-patient:Alle in der Liste referenzierten Patienten müssen gleich sein {entry.item.resolve().ofType(MedicationRequest).all(subject.identifier.system = %context.subject.identifier.system and subject.identifier.value = %context.subject.identifier.value)}</t>
   </si>
   <si>
     <t>Act[classCode&lt;ORG,moodCode=EVN]</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3782" uniqueCount="509">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1406,20 +1406,6 @@
   </si>
   <si>
     <t>List.entry.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1943,7 +1929,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4145,7 +4131,7 @@
         <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -10185,14 +10171,14 @@
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -10207,17 +10193,13 @@
         <v>106</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>212</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10265,7 +10247,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10280,7 +10262,7 @@
         <v>114</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
@@ -10288,10 +10270,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10317,16 +10299,16 @@
         <v>246</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10355,7 +10337,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -10373,7 +10355,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10396,10 +10378,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10502,10 +10484,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10610,10 +10592,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10720,10 +10702,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10826,10 +10808,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10934,10 +10916,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11044,10 +11026,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11152,10 +11134,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11260,10 +11242,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11368,10 +11350,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11478,10 +11460,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11588,10 +11570,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11617,82 +11599,82 @@
         <v>294</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q90" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="R90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI90" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q90" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="R90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>21</v>
@@ -11700,10 +11682,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11729,14 +11711,14 @@
         <v>396</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -11785,7 +11767,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -11800,7 +11782,7 @@
         <v>97</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
@@ -11808,10 +11790,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11834,13 +11816,13 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11891,7 +11873,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>85</v>
@@ -11906,7 +11888,7 @@
         <v>97</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
@@ -11914,10 +11896,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12020,10 +12002,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12128,10 +12110,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12236,10 +12218,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12344,10 +12326,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12452,10 +12434,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12560,10 +12542,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12589,16 +12571,16 @@
         <v>246</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -12627,7 +12609,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
@@ -12645,7 +12627,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -12660,7 +12642,7 @@
         <v>97</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>21</v>
@@ -12668,10 +12650,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12774,10 +12756,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12882,10 +12864,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12992,10 +12974,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13098,10 +13080,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13206,10 +13188,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13316,10 +13298,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13424,10 +13406,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13532,10 +13514,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13640,10 +13622,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13750,10 +13732,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1426,7 +1426,7 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEntryFlagVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-listentryflag-vs</t>
   </si>
   <si>
     <t>List.entry.flag.id</t>
@@ -1551,7 +1551,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-listemptyreason-vs</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1940,7 +1940,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
